--- a/sources/ganryu_step3.xlsx
+++ b/sources/ganryu_step3.xlsx
@@ -690,6 +690,11 @@
           <t>Opponent can tech roll after the throw.</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2a7ac50b-41fc-4e71-b0c5-5b89e00a22db</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>2a7ac50b-41fc-4e71-b0c5-5b89e00a22db</t>
@@ -727,6 +732,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>772009bb-1ba2-4bed-a93b-b143fc09bbac</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>772009bb-1ba2-4bed-a93b-b143fc09bbac</t>
@@ -764,6 +774,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3a4f81fa-8568-40b0-912f-e46ef9153678</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>3a4f81fa-8568-40b0-912f-e46ef9153678</t>
@@ -801,6 +816,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5bc9fb38-18e7-401d-903c-7e16457c54ea</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>5bc9fb38-18e7-401d-903c-7e16457c54ea</t>
@@ -836,6 +856,11 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>06da1e67-d557-429d-bbe8-0414aa87e38a</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
